--- a/tests/TC-13/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-13/results/timetable_all_departments_even.xlsx
@@ -78,8 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DFF3D6"/>
-        <bgColor rgb="00DFF3D6"/>
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,8 +96,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFD6D6"/>
+        <bgColor rgb="00FFD6D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,14 +108,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4C3"/>
-        <bgColor rgb="00F0F4C3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD0E6"/>
-        <bgColor rgb="00FFD0E6"/>
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,8 +120,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-        <bgColor rgb="00FFF3BF"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,8 +132,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD6D6"/>
-        <bgColor rgb="00FFD6D6"/>
+        <fgColor rgb="00DFF3D6"/>
+        <bgColor rgb="00DFF3D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4C3"/>
+        <bgColor rgb="00F0F4C3"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,14 +191,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -233,17 +233,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -279,10 +279,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,19 +297,13 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -911,350 +911,343 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>NEW
-TUT
-Room: 115
-TBD</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 110
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 102
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="13" t="inlineStr"/>
-      <c r="L2" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="13" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 109
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="13" t="inlineStr"/>
-      <c r="R2" s="16" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 104
-Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>NEW
-TUT
-Room: 115
-TBD</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="13" t="inlineStr"/>
-      <c r="I3" s="13" t="inlineStr"/>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>EC155
-TUT
-Room: 119
-TBD</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
           <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="13" t="inlineStr"/>
-      <c r="P3" s="13" t="inlineStr"/>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 102
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="13" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>CS151
-TUT
-Room: 102
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 109
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="13" t="inlineStr"/>
-      <c r="P4" s="20" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 117
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="13" t="inlineStr"/>
-      <c r="T4" s="21" t="inlineStr">
-        <is>
-          <t>DA151
-TUT
-Room: 110
-Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>CS163
 LEC
 Room: 109
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>CS162
 LEC
-Room: 101
+Room: 118
 Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="13" t="inlineStr"/>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 107
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="n"/>
+      <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>HS159
+TUT
+Room: 113
+TBD</t>
+        </is>
+      </c>
+      <c r="S2" s="9" t="n"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 117
+Dr. Anand Barangi</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>DS151
 LEC
-Room: 117
+Room: 113
 Dr. Shrishendu Layek</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="13" t="inlineStr"/>
-      <c r="T5" s="22" t="inlineStr">
-        <is>
-          <t>HS159
-TUT
-Room: 108
-TBD</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 120
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>CS163
 LEC
 Room: 109
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="13" t="inlineStr"/>
-      <c r="P6" s="19" t="inlineStr">
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>CS151
 LEC
-Room: 106
+Room: 119
 Dr. Rajendra H</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="13" t="inlineStr"/>
-      <c r="T6" s="13" t="inlineStr"/>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="10" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 118
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>DA151
+TUT
+Room: 115
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 109
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>DS151
+TUT
+Room: 113
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 113
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>CS162
+TUT
+Room: 113
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>CS151
+TUT
+Room: 119
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 109
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>NEW
+TUT
+Room: 111
+TBD</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 107
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="10" t="inlineStr"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>EC155
+TUT
+Room: 104
+TBD</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1324,7 +1317,7 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1345,7 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1373,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1401,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1429,7 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1457,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1485,7 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1513,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1541,7 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1569,7 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -1604,30 +1597,32 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>117</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:G3"/>
+  <mergeCells count="21">
+    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N6:P6"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="D6:G6"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="P6:R6"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1787,350 +1782,343 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>NEW
-TUT
-Room: 115
-TBD</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 110
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 102
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="13" t="inlineStr"/>
-      <c r="L2" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="13" t="inlineStr"/>
-      <c r="N2" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 109
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="13" t="inlineStr"/>
-      <c r="R2" s="16" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 104
-Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>NEW
-TUT
-Room: 115
-TBD</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="13" t="inlineStr"/>
-      <c r="I3" s="13" t="inlineStr"/>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>EC155
-TUT
-Room: 119
-TBD</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
           <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="13" t="inlineStr"/>
-      <c r="P3" s="13" t="inlineStr"/>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 102
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="13" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>CS151
-TUT
-Room: 102
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 109
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="13" t="inlineStr"/>
-      <c r="P4" s="20" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 117
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="13" t="inlineStr"/>
-      <c r="T4" s="21" t="inlineStr">
-        <is>
-          <t>DA151
-TUT
-Room: 110
-Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="13" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>CS163
 LEC
 Room: 109
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
-      <c r="K5" s="13" t="inlineStr"/>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>CS162
 LEC
-Room: 101
+Room: 118
 Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="13" t="inlineStr"/>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 107
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="n"/>
+      <c r="P2" s="9" t="n"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>HS159
+TUT
+Room: 113
+TBD</t>
+        </is>
+      </c>
+      <c r="S2" s="9" t="n"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 117
+Dr. Anand Barangi</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>DS151
 LEC
-Room: 117
+Room: 113
 Dr. Shrishendu Layek</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="13" t="inlineStr"/>
-      <c r="T5" s="22" t="inlineStr">
-        <is>
-          <t>HS159
-TUT
-Room: 108
-TBD</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 120
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>CS165/CS201
-LEC
-Room: 102
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="13" t="inlineStr"/>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>CS163
 LEC
 Room: 109
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="13" t="inlineStr"/>
-      <c r="P6" s="19" t="inlineStr">
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="12" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>CS151
 LEC
-Room: 106
+Room: 119
 Dr. Rajendra H</t>
         </is>
       </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="13" t="inlineStr"/>
-      <c r="T6" s="13" t="inlineStr"/>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="10" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 118
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>DA151
+TUT
+Room: 115
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 109
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t>DS151
+TUT
+Room: 113
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 113
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>CS162
+TUT
+Room: 113
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>CS151
+TUT
+Room: 119
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 109
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 115
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>NEW
+TUT
+Room: 111
+TBD</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 107
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="10" t="inlineStr"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>EC155
+TUT
+Room: 104
+TBD</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -2200,7 +2188,7 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2216,7 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2244,7 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2272,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2300,7 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2328,7 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2356,7 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2384,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2412,7 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>104</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2440,7 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -2480,30 +2468,32 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>117</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:G3"/>
+  <mergeCells count="21">
+    <mergeCell ref="Q5:S5"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="N6:P6"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="D6:G6"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="P4:R4"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="P6:R6"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2516,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2571,29 +2561,29 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -2607,19 +2597,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2629,7 +2619,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2640,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2665,7 +2655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2676,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Anand Barangi</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2701,7 +2691,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -2715,19 +2705,19 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2737,7 +2727,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2751,29 +2741,29 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>EC155</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2784,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2809,7 +2799,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2820,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2845,7 +2835,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2866,12 +2856,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2881,7 +2871,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2892,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Prof. S R M Prasanna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2917,7 +2907,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>DA151</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2928,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2953,7 +2943,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2964,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2989,7 +2979,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3000,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3025,7 +3015,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3039,29 +3029,29 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
         <v>7</v>
       </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3075,29 +3065,29 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3111,19 +3101,19 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3133,7 +3123,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3134,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3169,7 +3159,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3183,19 +3173,19 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3219,101 +3209,101 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSE_4_B</t>
+          <t>CSE_4_A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSE_4_B</t>
+          <t>CSE_4_A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>EC155</t>
         </is>
       </c>
     </row>
@@ -3327,14 +3317,14 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3349,7 +3339,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3363,29 +3353,29 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Anand Barangi</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3386,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3421,7 +3411,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -3432,13 +3422,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3447,7 +3437,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3457,7 +3447,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>EC155</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -3471,19 +3461,19 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3493,7 +3483,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3507,19 +3497,19 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3529,7 +3519,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3540,22 +3530,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3565,7 +3555,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3576,32 +3566,32 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3615,19 +3605,19 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3637,7 +3627,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3651,29 +3641,29 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Prof. S R M Prasanna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>DA151</t>
         </is>
       </c>
     </row>
@@ -3684,13 +3674,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3699,7 +3689,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3720,13 +3710,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3735,7 +3725,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3759,19 +3749,19 @@
         <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3781,7 +3771,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3795,29 +3785,29 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3828,32 +3818,32 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3854,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
         <v>13</v>
@@ -3889,7 +3879,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3900,32 +3890,176 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" t="n">
+        <v>17</v>
+      </c>
+      <c r="D39" t="n">
+        <v>19</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>6</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" t="n">
         <v>16</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CS208</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CSE_4_B</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
         <v>18</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>CS151</t>
+      <c r="D43" t="n">
+        <v>19</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>EC155</t>
         </is>
       </c>
     </row>

--- a/tests/TC-13/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-13/results/timetable_all_departments_even.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -78,14 +78,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0E6"/>
-        <bgColor rgb="00FFD0E6"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,32 +102,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD6D6"/>
-        <bgColor rgb="00FFD6D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD6D1"/>
-        <bgColor rgb="00FFD6D1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF3BF"/>
         <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E1BEE7"/>
-        <bgColor rgb="00E1BEE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,14 +120,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DFF3D6"/>
-        <bgColor rgb="00DFF3D6"/>
+        <fgColor rgb="00F0F4C3"/>
+        <bgColor rgb="00F0F4C3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F4C3"/>
-        <bgColor rgb="00F0F4C3"/>
+        <fgColor rgb="00FFD6D6"/>
+        <bgColor rgb="00FFD6D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,14 +179,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -207,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,13 +203,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,22 +221,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -263,32 +251,29 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,16 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -765,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -911,719 +887,662 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
+          <t>CS162
+TUT
+Room: 107
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr"/>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>CS151
+TUT
+Room: 108
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 116
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="12" t="inlineStr"/>
+      <c r="P2" s="12" t="inlineStr"/>
+      <c r="Q2" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 110
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 110
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>CS151
+LEC
+Room: 101
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 116
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
           <t>CS165/CS201
 LEC
-Room: 109
+Room: 119
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 119
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>CS162
 LEC
-Room: 118
+Room: 105
 Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="12" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
-        <is>
-          <t>CS208
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>CS151
 LEC
-Room: 107
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="15" t="inlineStr">
+Room: 101
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="12" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr"/>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="12" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>DA151
+TUT
+Room: 120
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 119
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+TUT
+Room: 117
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="12" t="inlineStr"/>
+      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 105
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="12" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>EC155
+TUT
+Room: 113
+TBD_EC155</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>HS159
 TUT
-Room: 113
-TBD</t>
-        </is>
-      </c>
-      <c r="S2" s="9" t="n"/>
-      <c r="T2" s="16" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 117
-Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr">
+Room: 102
+TBD_HS159</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>CS165/CS201
 LEC
-Room: 109
+Room: 119
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>CS151
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="12" t="inlineStr"/>
+      <c r="P6" s="12" t="inlineStr"/>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>DA151
 LEC
-Room: 119
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="n"/>
-      <c r="O3" s="10" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="R3" s="12" t="n"/>
-      <c r="S3" s="9" t="n"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
+Room: 104
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="12" t="inlineStr"/>
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 118
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>DA151
-TUT
-Room: 115
-Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 109
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="9" t="n"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 113
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>CS151
-TUT
-Room: 119
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 109
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="10" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>NEW
-TUT
-Room: 111
-TBD</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="14" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 107
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="22" t="inlineStr">
-        <is>
-          <t>EC155
-TUT
-Room: 104
-TBD</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="10" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>CS162</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr"/>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr"/>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>118</t>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>CS163</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr"/>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr"/>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Data Structures and Algorithms</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>3-0-2-0-4</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>115</t>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>CS208</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr"/>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr"/>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Computer Architecture</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>3-0-2-0-2</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>107</t>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>CS165/CS201</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr"/>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr"/>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Mathematical Foundations of Computing/Discrete Mathematics</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>3-0-0-0-3</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>109</t>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>DS151</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr"/>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr"/>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Linux for Engineers</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>CS151</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Introduction to Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>DA151</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr"/>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Analytics</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>HS159</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr"/>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Principles of Quantum Physics</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>TBD_HS159</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>EC155</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr"/>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Fundamentals of Sensing and Control-II</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>TBD_EC155</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>CS151</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr"/>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>Introduction to Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>DA151</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr"/>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>Introduction to Financial Analytics</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>HS159</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr"/>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Principles of Quantum Physics</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>EC155</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="inlineStr"/>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>Fundamentals of Sensing and Control-II</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr"/>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>Consumer Psychology and Decision Making</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>MA163</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="inlineStr"/>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>Linear Algebra</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="N2:P2"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="Q4:S4"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="M2:N2"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="M6:N6"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="D6:G6"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="D2:G2"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1636,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1782,719 +1701,662 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
+          <t>CS162
+TUT
+Room: 107
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="12" t="inlineStr"/>
+      <c r="I2" s="12" t="inlineStr"/>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>CS151
+TUT
+Room: 108
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 116
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="12" t="inlineStr"/>
+      <c r="P2" s="12" t="inlineStr"/>
+      <c r="Q2" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 110
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="12" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 110
+Dr. Swagatika Sahoo</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="12" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>CS151
+LEC
+Room: 101
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+LEC
+Room: 116
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="12" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="17" t="inlineStr">
+        <is>
           <t>CS165/CS201
 LEC
-Room: 109
+Room: 119
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
+      <c r="T3" s="12" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 119
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>CS162
 LEC
-Room: 118
+Room: 105
 Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="G2" s="12" t="n"/>
-      <c r="H2" s="12" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="14" t="inlineStr">
-        <is>
-          <t>CS208
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>CS151
 LEC
-Room: 107
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="15" t="inlineStr">
+Room: 101
+Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="12" t="inlineStr"/>
+      <c r="P4" s="12" t="inlineStr"/>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="12" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>DA151
+TUT
+Room: 120
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr"/>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>CS165/CS201
+LEC
+Room: 119
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="12" t="inlineStr"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>DS151
+TUT
+Room: 117
+Dr. Shrishendu Layek</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="12" t="inlineStr"/>
+      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 105
+Dr. Dibyajyoti Guha</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="12" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>EC155
+TUT
+Room: 113
+TBD_EC155</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 117
+Dr. Suvadip Hazra</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>HS159
 TUT
-Room: 113
-TBD</t>
-        </is>
-      </c>
-      <c r="S2" s="9" t="n"/>
-      <c r="T2" s="16" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 117
-Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr">
+Room: 102
+TBD_HS159</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>CS165/CS201
 LEC
-Room: 109
+Room: 119
 Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>CS151
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="12" t="inlineStr"/>
+      <c r="P6" s="12" t="inlineStr"/>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>DA151
 LEC
-Room: 119
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="n"/>
-      <c r="O3" s="10" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="R3" s="12" t="n"/>
-      <c r="S3" s="9" t="n"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
+Room: 104
+Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="12" t="inlineStr"/>
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 118
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="20" t="inlineStr">
-        <is>
-          <t>DA151
-TUT
-Room: 115
-Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 109
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="Q4" s="12" t="n"/>
-      <c r="R4" s="9" t="n"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-TUT
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>DS151
-LEC
-Room: 113
-Dr. Shrishendu Layek</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 113
-Dr. Dibyajyoti Guha</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t>CS151
-TUT
-Room: 119
-Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>CS165/CS201
-LEC
-Room: 109
-Dr. Suvadip Hazra</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="9" t="n"/>
-      <c r="T5" s="10" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 115
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>NEW
-TUT
-Room: 111
-TBD</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="14" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 107
-Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="22" t="inlineStr">
-        <is>
-          <t>EC155
-TUT
-Room: 104
-TBD</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="10" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>CS162</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr"/>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr"/>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>118</t>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>CS163</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr"/>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr"/>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Data Structures and Algorithms</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>3-0-2-0-4</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>115</t>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>CS208</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr"/>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr"/>
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>Computer Architecture</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>3-0-2-0-2</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>107</t>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>CS165/CS201</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr"/>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr"/>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Mathematical Foundations of Computing/Discrete Mathematics</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>3-0-0-0-3</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>109</t>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>DS151</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr"/>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr"/>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Linux for Engineers</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>CS151</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr"/>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Introduction to Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra H</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>DA151</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr"/>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Introduction to Financial Analytics</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Prof. S R M Prasanna</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>HS159</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr"/>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Principles of Quantum Physics</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>TBD_HS159</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>EC155</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr"/>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Fundamentals of Sensing and Control-II</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>TBD_EC155</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>CS151</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr"/>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>Introduction to Cybersecurity</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>Dr. Rajendra H</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>DA151</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr"/>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>Introduction to Financial Analytics</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>Prof. S R M Prasanna</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>HS159</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr"/>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>Principles of Quantum Physics</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>EC155</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="inlineStr"/>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>Fundamentals of Sensing and Control-II</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="inlineStr"/>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>Consumer Psychology and Decision Making</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>MA163</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="inlineStr"/>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>Linear Algebra</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Dr. Anand Barangi</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>3-1-0-0-2</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="N2:P2"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="Q4:S4"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="M2:N2"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="M6:N6"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="D6:G6"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="D2:G2"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E6:H6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2506,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2561,19 +2423,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2583,7 +2445,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2597,29 +2459,29 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2633,19 +2495,19 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
         <v>14</v>
       </c>
-      <c r="D4" t="n">
-        <v>16</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2655,7 +2517,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2669,29 +2531,29 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
         <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2574,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2727,7 +2589,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2610,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2763,7 +2625,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2646,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2799,7 +2661,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2687,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2835,7 +2697,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -2849,19 +2711,19 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2871,7 +2733,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -2885,29 +2747,29 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prof. S R M Prasanna</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA151</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2790,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2943,7 +2805,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2957,10 +2819,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2969,7 +2831,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2993,19 +2855,19 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3015,7 +2877,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3029,19 +2891,19 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3051,7 +2913,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3065,29 +2927,29 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3101,19 +2963,19 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3123,7 +2985,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3134,22 +2996,22 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>17</v>
-      </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3173,29 +3035,29 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>TBD_HS159</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -3209,29 +3071,29 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3245,19 +3107,19 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Swagatika Sahoo</t>
+          <t>Prof. S R M Prasanna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3267,43 +3129,43 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>DA151</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSE_4_A</t>
+          <t>CSE_4_B</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>EC155</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3317,29 +3179,29 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3353,19 +3215,19 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3375,7 +3237,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3389,10 +3251,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3401,7 +3263,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3422,32 +3284,32 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Swagatika Sahoo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -3461,19 +3323,19 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dr. Shrishendu Layek</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3483,7 +3345,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3497,19 +3359,19 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dr. Suvadip Hazra</t>
+          <t>Dr. Shrishendu Layek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3519,7 +3381,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3533,14 +3395,14 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3555,7 +3417,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3566,13 +3428,13 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
         <v>3</v>
       </c>
-      <c r="C30" t="n">
-        <v>17</v>
-      </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3581,7 +3443,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3591,7 +3453,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3605,10 +3467,10 @@
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3617,7 +3479,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3641,29 +3503,29 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prof. S R M Prasanna</t>
+          <t>Dr. Rajendra H</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DA151</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3677,10 +3539,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3689,7 +3551,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3699,7 +3561,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3710,13 +3572,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3725,7 +3587,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3735,7 +3597,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3749,10 +3611,10 @@
         <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3761,12 +3623,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3785,29 +3647,29 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dr. Dibyajyoti Guha</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3821,29 +3683,29 @@
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dr. Rajendra H</t>
+          <t>Dr. Dibyajyoti Guha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3854,13 +3716,13 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
         <v>5</v>
       </c>
-      <c r="C38" t="n">
-        <v>13</v>
-      </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3869,7 +3731,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3879,7 +3741,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CS165/CS201</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3890,32 +3752,32 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>TBD_HS159</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -3929,19 +3791,19 @@
         <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Suvadip Hazra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3951,7 +3813,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS165/CS201</t>
         </is>
       </c>
     </row>
@@ -3965,101 +3827,29 @@
         <v>6</v>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Prof. S R M Prasanna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" t="n">
-        <v>14</v>
-      </c>
-      <c r="D42" t="n">
-        <v>16</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Dr. Swagatika Sahoo</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>CS208</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CSE_4_B</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" t="n">
-        <v>18</v>
-      </c>
-      <c r="D43" t="n">
-        <v>19</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>EC155</t>
+          <t>DA151</t>
         </is>
       </c>
     </row>
